--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_engineering_construction.xlsx
@@ -594,16 +594,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.2250996015936255</v>
+        <v>0.01898058252427184</v>
       </c>
       <c r="J2">
-        <v>0.1544661291442787</v>
+        <v>0.01334080159322878</v>
       </c>
       <c r="K2">
-        <v>4.33</v>
+        <v>0.466</v>
       </c>
       <c r="L2">
-        <v>0.1725099601593625</v>
+        <v>0.02262135922330097</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,10 +633,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.07898795377422792</v>
+        <v>0.1280295319845063</v>
       </c>
       <c r="AB2">
-        <v>0.07898795377422792</v>
+        <v>0.1280295319845063</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.528</v>
+        <v>-0.223</v>
       </c>
       <c r="AQ2">
-        <v>-10.70075757575758</v>
+        <v>-1.753363228699552</v>
       </c>
     </row>
     <row r="3">
@@ -689,16 +689,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.2250996015936255</v>
+        <v>0.01898058252427184</v>
       </c>
       <c r="J3">
-        <v>0.1544661291442787</v>
+        <v>0.01334080159322878</v>
       </c>
       <c r="K3">
-        <v>4.33</v>
+        <v>0.466</v>
       </c>
       <c r="L3">
-        <v>0.1725099601593625</v>
+        <v>0.02262135922330097</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -728,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.07898795377422792</v>
+        <v>0.1280295319845063</v>
       </c>
       <c r="AB3">
-        <v>0.07898795377422792</v>
+        <v>0.1280295319845063</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.528</v>
+        <v>-0.223</v>
       </c>
       <c r="AQ3">
-        <v>-10.70075757575758</v>
+        <v>-1.753363228699552</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_engineering_construction.xlsx
@@ -587,6 +587,9 @@
           <t>Engineering/Construction</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.144</v>
+      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -594,16 +597,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01898058252427184</v>
+        <v>-0.1976331360946746</v>
       </c>
       <c r="J2">
-        <v>0.01334080159322878</v>
+        <v>-0.1976331360946746</v>
       </c>
       <c r="K2">
-        <v>0.466</v>
+        <v>-3.25</v>
       </c>
       <c r="L2">
-        <v>0.02262135922330097</v>
+        <v>-0.1923076923076923</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,22 +624,28 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.4230392156862746</v>
+      </c>
+      <c r="W2">
+        <v>-0.6298449612403101</v>
       </c>
       <c r="X2">
-        <v>0.1280295319845063</v>
+        <v>0.115385991782394</v>
+      </c>
+      <c r="Y2">
+        <v>-0.745230953022704</v>
       </c>
       <c r="AB2">
-        <v>0.1280295319845063</v>
+        <v>0.115385991782394</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,22 +657,28 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>-0.7332200509770606</v>
+      </c>
+      <c r="AK2">
+        <v>1.569090909090909</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.223</v>
+        <v>-0.279</v>
       </c>
       <c r="AQ2">
-        <v>-1.753363228699552</v>
+        <v>11.97132616487455</v>
       </c>
     </row>
     <row r="3">
@@ -682,6 +697,9 @@
           <t>Engineering/Construction</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.144</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -689,16 +707,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01898058252427184</v>
+        <v>-0.1976331360946746</v>
       </c>
       <c r="J3">
-        <v>0.01334080159322878</v>
+        <v>-0.1976331360946746</v>
       </c>
       <c r="K3">
-        <v>0.466</v>
+        <v>-3.25</v>
       </c>
       <c r="L3">
-        <v>0.02262135922330097</v>
+        <v>-0.1923076923076923</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -707,7 +725,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -716,22 +734,28 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.4230392156862746</v>
+      </c>
+      <c r="W3">
+        <v>-0.6298449612403101</v>
       </c>
       <c r="X3">
-        <v>0.1280295319845063</v>
+        <v>0.115385991782394</v>
+      </c>
+      <c r="Y3">
+        <v>-0.745230953022704</v>
       </c>
       <c r="AB3">
-        <v>0.1280295319845063</v>
+        <v>0.115385991782394</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -743,22 +767,28 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.7332200509770606</v>
+      </c>
+      <c r="AK3">
+        <v>1.569090909090909</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.223</v>
+        <v>-0.279</v>
       </c>
       <c r="AQ3">
-        <v>-1.753363228699552</v>
+        <v>11.97132616487455</v>
       </c>
     </row>
   </sheetData>
